--- a/exports/trend_1d/TMPV_full_report.xlsx
+++ b/exports/trend_1d/TMPV_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.27</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>385.3</v>
+        <v>373.6</v>
       </c>
       <c r="I2" t="n">
         <v>378.4256191136491</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>1.81</v>
       </c>
       <c r="L2" t="n">
         <v>1.99</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42256</v>
+        <v>42257</v>
       </c>
       <c r="H3" t="n">
-        <v>237.45</v>
+        <v>243.8</v>
       </c>
       <c r="I3" t="n">
         <v>243.5656103190935</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K3" t="n">
-        <v>36.44</v>
+        <v>34.74</v>
       </c>
       <c r="L3" t="n">
         <v>10.76</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>17.15</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42271</v>
+        <v>42275</v>
       </c>
       <c r="H4" t="n">
-        <v>208.9</v>
+        <v>196.2</v>
       </c>
       <c r="I4" t="n">
         <v>206.7554172122837</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-14.32</v>
+        <v>-19.52</v>
       </c>
       <c r="L4" t="n">
-        <v>14.83</v>
+        <v>19.93</v>
       </c>
       <c r="M4" t="n">
         <v>2.62</v>
       </c>
       <c r="N4" t="n">
-        <v>4.79</v>
+        <v>6.08</v>
       </c>
       <c r="O4" t="n">
         <v>2.67</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>18.34</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42282</v>
+        <v>42283</v>
       </c>
       <c r="H5" t="n">
-        <v>216.95</v>
+        <v>229.75</v>
       </c>
       <c r="I5" t="n">
         <v>227.6218077245487</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.58</v>
+        <v>-17.1</v>
       </c>
       <c r="L5" t="n">
-        <v>13.02</v>
+        <v>17.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="N5" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="O5" t="n">
         <v>-6.08</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.78</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42348</v>
+        <v>42349</v>
       </c>
       <c r="H6" t="n">
-        <v>268.25</v>
+        <v>260.2</v>
       </c>
       <c r="I6" t="n">
         <v>264.6148648026897</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K6" t="n">
-        <v>16.76</v>
+        <v>13.25</v>
       </c>
       <c r="L6" t="n">
         <v>4.24</v>
@@ -783,7 +854,7 @@
         <v>5.59</v>
       </c>
       <c r="N6" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>5.9</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.66</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H7" t="n">
-        <v>218.3</v>
+        <v>231.8</v>
       </c>
       <c r="I7" t="n">
         <v>229.2178329243565</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7" t="n">
-        <v>16.1</v>
+        <v>10.91</v>
       </c>
       <c r="L7" t="n">
         <v>6.63</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>15.79</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H8" t="n">
-        <v>282.05</v>
+        <v>262.85</v>
       </c>
       <c r="I8" t="n">
         <v>263.5273570686994</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K8" t="n">
-        <v>21.68</v>
+        <v>13.4</v>
       </c>
       <c r="L8" t="n">
         <v>4.51</v>
@@ -897,7 +992,7 @@
         <v>1.78</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>6.81</v>
       </c>
       <c r="O8" t="n">
         <v>6.18</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>13.68</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42517</v>
+        <v>42520</v>
       </c>
       <c r="H9" t="n">
-        <v>278.1</v>
+        <v>290.05</v>
       </c>
       <c r="I9" t="n">
         <v>288.4539625873367</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.8</v>
+        <v>-10.35</v>
       </c>
       <c r="L9" t="n">
-        <v>6.22</v>
+        <v>10.96</v>
       </c>
       <c r="M9" t="n">
         <v>1.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
         <v>-6.81</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42548</v>
+        <v>42549</v>
       </c>
       <c r="H10" t="n">
-        <v>309.1</v>
+        <v>303.2</v>
       </c>
       <c r="I10" t="n">
         <v>305.6445203832124</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>6.57</v>
+        <v>4.53</v>
       </c>
       <c r="L10" t="n">
         <v>4.74</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42569</v>
+        <v>42570</v>
       </c>
       <c r="H11" t="n">
-        <v>339.2</v>
+        <v>343.75</v>
       </c>
       <c r="I11" t="n">
         <v>340.5860721589169</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.87</v>
+        <v>-13.37</v>
       </c>
       <c r="L11" t="n">
         <v>14.68</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42636</v>
+        <v>42639</v>
       </c>
       <c r="H12" t="n">
-        <v>380.75</v>
+        <v>368.55</v>
       </c>
       <c r="I12" t="n">
         <v>372.8832512273756</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K12" t="n">
-        <v>10.76</v>
+        <v>7.21</v>
       </c>
       <c r="L12" t="n">
         <v>4.76</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42734</v>
+        <v>42737</v>
       </c>
       <c r="H13" t="n">
-        <v>324.95</v>
+        <v>335.35</v>
       </c>
       <c r="I13" t="n">
         <v>334.8350652975556</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K13" t="n">
-        <v>11.83</v>
+        <v>9.01</v>
       </c>
       <c r="L13" t="n">
         <v>6.69</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.26</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42772</v>
+        <v>42773</v>
       </c>
       <c r="H14" t="n">
-        <v>362.05</v>
+        <v>348.95</v>
       </c>
       <c r="I14" t="n">
         <v>352.0728168507637</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K14" t="n">
-        <v>7.96</v>
+        <v>4.06</v>
       </c>
       <c r="L14" t="n">
         <v>3.7</v>
@@ -1239,7 +1406,7 @@
         <v>0.86</v>
       </c>
       <c r="N14" t="n">
-        <v>1.98</v>
+        <v>3.62</v>
       </c>
       <c r="O14" t="n">
         <v>3.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H15" t="n">
-        <v>310.15</v>
+        <v>323.3</v>
       </c>
       <c r="I15" t="n">
         <v>313.6060040102188</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K15" t="n">
-        <v>11.12</v>
+        <v>7.35</v>
       </c>
       <c r="L15" t="n">
         <v>3.54</v>
       </c>
       <c r="M15" t="n">
-        <v>2.52</v>
+        <v>4.34</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>4.24</v>
       </c>
       <c r="O15" t="n">
         <v>-3.62</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>8.25</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42898</v>
+        <v>42899</v>
       </c>
       <c r="H16" t="n">
-        <v>314.15</v>
+        <v>309.5</v>
       </c>
       <c r="I16" t="n">
         <v>309.6238500567932</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.83</v>
+        <v>-4.27</v>
       </c>
       <c r="L16" t="n">
-        <v>3.42</v>
+        <v>4.59</v>
       </c>
       <c r="M16" t="n">
         <v>0.72</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.44</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42927</v>
+        <v>42928</v>
       </c>
       <c r="H17" t="n">
-        <v>314.6</v>
+        <v>317.4</v>
       </c>
       <c r="I17" t="n">
         <v>317.3812703807707</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.65</v>
+        <v>-2.55</v>
       </c>
       <c r="L17" t="n">
         <v>4.72</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.39</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42949</v>
+        <v>42950</v>
       </c>
       <c r="H18" t="n">
-        <v>303.2</v>
+        <v>297.05</v>
       </c>
       <c r="I18" t="n">
         <v>300.6318276665072</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.47</v>
+        <v>-6.41</v>
       </c>
       <c r="L18" t="n">
-        <v>4.96</v>
+        <v>6.81</v>
       </c>
       <c r="M18" t="n">
         <v>0.68</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>7.59</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42993</v>
+        <v>42996</v>
       </c>
       <c r="H19" t="n">
-        <v>276.6</v>
+        <v>278.8</v>
       </c>
       <c r="I19" t="n">
         <v>278.7012433942139</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K19" t="n">
-        <v>6.88</v>
+        <v>6.14</v>
       </c>
       <c r="L19" t="n">
         <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>1.47</v>
+        <v>2.51</v>
       </c>
       <c r="N19" t="n">
         <v>3.8</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.64</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43049</v>
+        <v>43052</v>
       </c>
       <c r="H20" t="n">
-        <v>290.95</v>
+        <v>287.85</v>
       </c>
       <c r="I20" t="n">
         <v>288.3702347058826</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K20" t="n">
-        <v>4.36</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
         <v>1.87</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.86</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43097</v>
+        <v>43098</v>
       </c>
       <c r="H21" t="n">
-        <v>288.2</v>
+        <v>297.35</v>
       </c>
       <c r="I21" t="n">
         <v>295.9867958136764</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.12</v>
+        <v>-3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>3.56</v>
+        <v>3.68</v>
       </c>
       <c r="M21" t="n">
         <v>1.73</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.26</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H22" t="n">
-        <v>287.8</v>
+        <v>277.9</v>
       </c>
       <c r="I22" t="n">
         <v>281.9393497401978</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.21</v>
+        <v>-6.54</v>
       </c>
       <c r="L22" t="n">
-        <v>5.04</v>
+        <v>6.78</v>
       </c>
       <c r="M22" t="n">
         <v>0.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>3.44</v>
       </c>
       <c r="O22" t="n">
         <v>3.17</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H23" t="n">
-        <v>244.85</v>
+        <v>249.35</v>
       </c>
       <c r="I23" t="n">
         <v>245.3209473721891</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K23" t="n">
-        <v>11.89</v>
+        <v>10.27</v>
       </c>
       <c r="L23" t="n">
         <v>3.13</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>8.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43213</v>
+        <v>43214</v>
       </c>
       <c r="H24" t="n">
-        <v>230</v>
+        <v>228.25</v>
       </c>
       <c r="I24" t="n">
         <v>229.2627364291067</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.76</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>8.18</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>1.75</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.57</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43329</v>
+        <v>43332</v>
       </c>
       <c r="H25" t="n">
-        <v>177.8</v>
+        <v>185.95</v>
       </c>
       <c r="I25" t="n">
         <v>185.7979767675103</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K25" t="n">
-        <v>22.1</v>
+        <v>18.53</v>
       </c>
       <c r="L25" t="n">
         <v>6.07</v>
@@ -1866,7 +2165,7 @@
         <v>2.58</v>
       </c>
       <c r="N25" t="n">
-        <v>3.98</v>
+        <v>4.58</v>
       </c>
       <c r="O25" t="n">
         <v>-0.76</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>10.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H26" t="n">
-        <v>173.9</v>
+        <v>172.35</v>
       </c>
       <c r="I26" t="n">
         <v>172.7329830209435</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.48</v>
+        <v>-7.31</v>
       </c>
       <c r="L26" t="n">
-        <v>7.21</v>
+        <v>15.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.23</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.66</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43409</v>
+        <v>43410</v>
       </c>
       <c r="H27" t="n">
-        <v>130.7</v>
+        <v>133.05</v>
       </c>
       <c r="I27" t="n">
         <v>132.7558951336021</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K27" t="n">
-        <v>24.17</v>
+        <v>22.8</v>
       </c>
       <c r="L27" t="n">
         <v>2.96</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>11.55</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43438</v>
+        <v>43439</v>
       </c>
       <c r="H28" t="n">
-        <v>121</v>
+        <v>116.5</v>
       </c>
       <c r="I28" t="n">
         <v>117.9705192588072</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.06</v>
+        <v>-12.44</v>
       </c>
       <c r="L28" t="n">
-        <v>12.03</v>
+        <v>12.74</v>
       </c>
       <c r="M28" t="n">
         <v>2.99</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.26</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43453</v>
+        <v>43454</v>
       </c>
       <c r="H29" t="n">
-        <v>119.75</v>
+        <v>121.45</v>
       </c>
       <c r="I29" t="n">
         <v>120.5993586274408</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.79</v>
+        <v>-4.25</v>
       </c>
       <c r="L29" t="n">
         <v>4.98</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43503</v>
+        <v>43504</v>
       </c>
       <c r="H30" t="n">
-        <v>125.9</v>
+        <v>103.75</v>
       </c>
       <c r="I30" t="n">
         <v>117.1174545353638</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K30" t="n">
-        <v>3.66</v>
+        <v>-14.57</v>
       </c>
       <c r="L30" t="n">
-        <v>6.42</v>
+        <v>26.88</v>
       </c>
       <c r="M30" t="n">
-        <v>1.63</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>2.93</v>
+        <v>17.59</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>19.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43521</v>
+        <v>43522</v>
       </c>
       <c r="H31" t="n">
-        <v>121</v>
+        <v>125.75</v>
       </c>
       <c r="I31" t="n">
         <v>123.5314159021831</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>-16.63</v>
+        <v>-21.2</v>
       </c>
       <c r="L31" t="n">
-        <v>17.78</v>
+        <v>21.73</v>
       </c>
       <c r="M31" t="n">
         <v>0.77</v>
       </c>
       <c r="N31" t="n">
-        <v>3.14</v>
+        <v>3.93</v>
       </c>
       <c r="O31" t="n">
         <v>-17.59</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.95</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H32" t="n">
-        <v>147.55</v>
+        <v>142.75</v>
       </c>
       <c r="I32" t="n">
         <v>144.5076778263034</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K32" t="n">
-        <v>17.34</v>
+        <v>13.52</v>
       </c>
       <c r="L32" t="n">
         <v>8.27</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.34</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H33" t="n">
-        <v>83.95</v>
+        <v>92.5</v>
       </c>
       <c r="I33" t="n">
         <v>89.38213845953727</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K33" t="n">
-        <v>41.19</v>
+        <v>35.2</v>
       </c>
       <c r="L33" t="n">
         <v>3.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9</v>
+        <v>4.17</v>
       </c>
       <c r="N33" t="n">
-        <v>8.869999999999999</v>
+        <v>10.18</v>
       </c>
       <c r="O33" t="n">
         <v>-3.25</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>20.01</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43857</v>
+        <v>43858</v>
       </c>
       <c r="H34" t="n">
-        <v>125.45</v>
+        <v>121.25</v>
       </c>
       <c r="I34" t="n">
         <v>123.6012042870484</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K34" t="n">
-        <v>35.62</v>
+        <v>31.08</v>
       </c>
       <c r="L34" t="n">
         <v>16.16</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.36</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H35" t="n">
-        <v>53.8</v>
+        <v>64.2</v>
       </c>
       <c r="I35" t="n">
         <v>58.71386241661708</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K35" t="n">
-        <v>55.63</v>
+        <v>47.05</v>
       </c>
       <c r="L35" t="n">
         <v>9.32</v>
       </c>
       <c r="M35" t="n">
-        <v>5.59</v>
+        <v>10.04</v>
       </c>
       <c r="N35" t="n">
-        <v>10.87</v>
+        <v>19.33</v>
       </c>
       <c r="O35" t="n">
         <v>-3.35</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>22.04</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43997</v>
+        <v>43998</v>
       </c>
       <c r="H36" t="n">
-        <v>69.2</v>
+        <v>65.25</v>
       </c>
       <c r="I36" t="n">
         <v>68.15423914820079</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K36" t="n">
-        <v>7.79</v>
+        <v>1.64</v>
       </c>
       <c r="L36" t="n">
         <v>14.64</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>23.91</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44047</v>
+        <v>44048</v>
       </c>
       <c r="H37" t="n">
-        <v>76.75</v>
+        <v>79.45</v>
       </c>
       <c r="I37" t="n">
         <v>77.91632281355693</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
-        <v>-17.62</v>
+        <v>-21.76</v>
       </c>
       <c r="L37" t="n">
-        <v>21.46</v>
+        <v>24.14</v>
       </c>
       <c r="M37" t="n">
         <v>2.34</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.17</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H38" t="n">
-        <v>94.65000000000001</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>91.83497854408418</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K38" t="n">
-        <v>19.13</v>
+        <v>15.36</v>
       </c>
       <c r="L38" t="n">
         <v>2.96</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>15.54</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H39" t="n">
-        <v>97.09999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="I39" t="n">
         <v>99.63276299976353</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.95</v>
+        <v>-9.66</v>
       </c>
       <c r="L39" t="n">
-        <v>9.550000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="M39" t="n">
         <v>3.04</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>10.71</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H40" t="n">
-        <v>124.3</v>
+        <v>113.3</v>
       </c>
       <c r="I40" t="n">
         <v>114.31858948488</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>23.68</v>
+        <v>12.74</v>
       </c>
       <c r="L40" t="n">
         <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>1.21</v>
+        <v>2.49</v>
       </c>
       <c r="N40" t="n">
-        <v>3.22</v>
+        <v>8.85</v>
       </c>
       <c r="O40" t="n">
         <v>3.5</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>15.72</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44189</v>
+        <v>44193</v>
       </c>
       <c r="H41" t="n">
-        <v>121.15</v>
+        <v>128.3</v>
       </c>
       <c r="I41" t="n">
         <v>127.4094865122677</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.93</v>
+        <v>-13.24</v>
       </c>
       <c r="L41" t="n">
-        <v>8.16</v>
+        <v>13.86</v>
       </c>
       <c r="M41" t="n">
-        <v>1.63</v>
+        <v>2.23</v>
       </c>
       <c r="N41" t="n">
-        <v>3.99</v>
+        <v>5.9</v>
       </c>
       <c r="O41" t="n">
         <v>-8.85</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.27</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H42" t="n">
-        <v>220.3</v>
+        <v>210.55</v>
       </c>
       <c r="I42" t="n">
         <v>211.3258391498962</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K42" t="n">
-        <v>71.70999999999999</v>
+        <v>64.11</v>
       </c>
       <c r="L42" t="n">
         <v>3.94</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>15.32</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44327</v>
+        <v>44328</v>
       </c>
       <c r="H43" t="n">
-        <v>217.25</v>
+        <v>224.45</v>
       </c>
       <c r="I43" t="n">
         <v>222.6850953632338</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.18</v>
+        <v>-6.6</v>
       </c>
       <c r="L43" t="n">
-        <v>6.27</v>
+        <v>9.48</v>
       </c>
       <c r="M43" t="n">
         <v>2.1</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.84</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44382</v>
+        <v>44383</v>
       </c>
       <c r="H44" t="n">
-        <v>238.3</v>
+        <v>218.2</v>
       </c>
       <c r="I44" t="n">
         <v>221.7412723239505</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K44" t="n">
-        <v>6.17</v>
+        <v>-2.78</v>
       </c>
       <c r="L44" t="n">
         <v>6.1</v>
@@ -2949,7 +3476,7 @@
         <v>5.85</v>
       </c>
       <c r="N44" t="n">
-        <v>5.42</v>
+        <v>8.43</v>
       </c>
       <c r="O44" t="n">
         <v>3.31</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>17.32</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44452</v>
+        <v>44453</v>
       </c>
       <c r="H45" t="n">
-        <v>207.4</v>
+        <v>210.75</v>
       </c>
       <c r="I45" t="n">
         <v>208.9327095457496</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K45" t="n">
-        <v>4.95</v>
+        <v>3.41</v>
       </c>
       <c r="L45" t="n">
         <v>13.02</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.6</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H46" t="n">
-        <v>339.25</v>
+        <v>316.85</v>
       </c>
       <c r="I46" t="n">
         <v>325.1143162740606</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K46" t="n">
-        <v>60.97</v>
+        <v>50.34</v>
       </c>
       <c r="L46" t="n">
         <v>4.25</v>
       </c>
       <c r="M46" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="N46" t="n">
-        <v>5.43</v>
+        <v>6.6</v>
       </c>
       <c r="O46" t="n">
         <v>1.62</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>16.57</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H47" t="n">
-        <v>337.8</v>
+        <v>346.8</v>
       </c>
       <c r="I47" t="n">
         <v>344.899059749752</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.61</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L47" t="n">
         <v>10.04</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H48" t="n">
-        <v>345.5</v>
+        <v>329.4</v>
       </c>
       <c r="I48" t="n">
         <v>329.4532480640163</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.37</v>
+        <v>-5.02</v>
       </c>
       <c r="L48" t="n">
-        <v>2.47</v>
+        <v>6.03</v>
       </c>
       <c r="M48" t="n">
         <v>1.03</v>
       </c>
       <c r="N48" t="n">
-        <v>2.7</v>
+        <v>4.66</v>
       </c>
       <c r="O48" t="n">
         <v>2.66</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.61</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H49" t="n">
-        <v>307.6</v>
+        <v>315.35</v>
       </c>
       <c r="I49" t="n">
         <v>311.9213756009724</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K49" t="n">
-        <v>6.62</v>
+        <v>4.27</v>
       </c>
       <c r="L49" t="n">
         <v>8.68</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.02</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H50" t="n">
-        <v>293.5</v>
+        <v>281.3</v>
       </c>
       <c r="I50" t="n">
         <v>289.6993014418844</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.93</v>
+        <v>-10.8</v>
       </c>
       <c r="L50" t="n">
-        <v>8.960000000000001</v>
+        <v>11.15</v>
       </c>
       <c r="M50" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="N50" t="n">
-        <v>3.13</v>
+        <v>4.16</v>
       </c>
       <c r="O50" t="n">
         <v>2.52</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.2</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44697</v>
+        <v>44698</v>
       </c>
       <c r="H51" t="n">
-        <v>279.1</v>
+        <v>292.05</v>
       </c>
       <c r="I51" t="n">
         <v>290.2580450768252</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K51" t="n">
-        <v>0.78</v>
+        <v>-3.82</v>
       </c>
       <c r="L51" t="n">
-        <v>2.84</v>
+        <v>4.18</v>
       </c>
       <c r="M51" t="n">
         <v>3.94</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>15.16</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H52" t="n">
-        <v>285.1</v>
+        <v>270.55</v>
       </c>
       <c r="I52" t="n">
         <v>273.9825777793756</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.38</v>
+        <v>-7.36</v>
       </c>
       <c r="L52" t="n">
-        <v>6.59</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M52" t="n">
         <v>3.66</v>
       </c>
       <c r="N52" t="n">
-        <v>4.99</v>
+        <v>5.1</v>
       </c>
       <c r="O52" t="n">
         <v>4.64</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>14.47</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H53" t="n">
-        <v>286.65</v>
+        <v>296.65</v>
       </c>
       <c r="I53" t="n">
         <v>295.2057393419763</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.95</v>
+        <v>-9.65</v>
       </c>
       <c r="L53" t="n">
-        <v>7.89</v>
+        <v>10.18</v>
       </c>
       <c r="M53" t="n">
         <v>2.02</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44810</v>
+        <v>44811</v>
       </c>
       <c r="H54" t="n">
-        <v>315.15</v>
+        <v>306.95</v>
       </c>
       <c r="I54" t="n">
         <v>311.4338011799209</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K54" t="n">
-        <v>6.24</v>
+        <v>3.47</v>
       </c>
       <c r="L54" t="n">
         <v>2.68</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44869</v>
+        <v>44872</v>
       </c>
       <c r="H55" t="n">
-        <v>292.85</v>
+        <v>299.5</v>
       </c>
       <c r="I55" t="n">
         <v>294.9978755250264</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K55" t="n">
-        <v>4.59</v>
+        <v>2.43</v>
       </c>
       <c r="L55" t="n">
         <v>2.95</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.78</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H56" t="n">
-        <v>287.25</v>
+        <v>284.55</v>
       </c>
       <c r="I56" t="n">
         <v>285.4954680092073</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.09</v>
+        <v>-4.99</v>
       </c>
       <c r="L56" t="n">
         <v>5.93</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>6.55</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44935</v>
+        <v>44936</v>
       </c>
       <c r="H57" t="n">
-        <v>268.15</v>
+        <v>284.3</v>
       </c>
       <c r="I57" t="n">
         <v>283.1219006549235</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K57" t="n">
-        <v>5.76</v>
+        <v>0.09</v>
       </c>
       <c r="L57" t="n">
         <v>3.51</v>
       </c>
       <c r="M57" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="N57" t="n">
-        <v>2.42</v>
+        <v>6.02</v>
       </c>
       <c r="O57" t="n">
         <v>-0.9399999999999999</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.94</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H58" t="n">
-        <v>286.85</v>
+        <v>283.2</v>
       </c>
       <c r="I58" t="n">
         <v>284.1919063146672</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9</v>
+        <v>-0.39</v>
       </c>
       <c r="L58" t="n">
         <v>3.13</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H59" t="n">
-        <v>293.7</v>
+        <v>301.3</v>
       </c>
       <c r="I59" t="n">
         <v>299.4848822776808</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.71</v>
+        <v>-6.39</v>
       </c>
       <c r="L59" t="n">
-        <v>4.24</v>
+        <v>6.8</v>
       </c>
       <c r="M59" t="n">
         <v>1.29</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.06</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45142</v>
+        <v>45145</v>
       </c>
       <c r="H60" t="n">
-        <v>423.45</v>
+        <v>419.65</v>
       </c>
       <c r="I60" t="n">
         <v>420.9603236547612</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K60" t="n">
-        <v>40.54</v>
+        <v>39.28</v>
       </c>
       <c r="L60" t="n">
         <v>3.17</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>7.4</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45211</v>
+        <v>45212</v>
       </c>
       <c r="H61" t="n">
-        <v>438.55</v>
+        <v>459.3</v>
       </c>
       <c r="I61" t="n">
         <v>441.2375553409611</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.5</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>6.15</v>
+        <v>9.76</v>
       </c>
       <c r="M61" t="n">
         <v>1.2</v>
       </c>
       <c r="N61" t="n">
-        <v>2.63</v>
+        <v>4.73</v>
       </c>
       <c r="O61" t="n">
         <v>-0.9</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.24</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H62" t="n">
-        <v>439.15</v>
+        <v>431.4</v>
       </c>
       <c r="I62" t="n">
         <v>433.4527219024126</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.39</v>
+        <v>-6.07</v>
       </c>
       <c r="L62" t="n">
-        <v>5.12</v>
+        <v>6.43</v>
       </c>
       <c r="M62" t="n">
         <v>0.83</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.7</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H63" t="n">
-        <v>462.35</v>
+        <v>468.45</v>
       </c>
       <c r="I63" t="n">
         <v>464.6219593727309</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.17</v>
+        <v>-8.59</v>
       </c>
       <c r="L63" t="n">
-        <v>7.49</v>
+        <v>9.4</v>
       </c>
       <c r="M63" t="n">
         <v>4.02</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.93</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H64" t="n">
-        <v>666.3</v>
+        <v>651.2</v>
       </c>
       <c r="I64" t="n">
         <v>659.1257095268772</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K64" t="n">
-        <v>42.24</v>
+        <v>39.01</v>
       </c>
       <c r="L64" t="n">
         <v>1.42</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>10.89</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H65" t="n">
-        <v>696.85</v>
+        <v>709.35</v>
       </c>
       <c r="I65" t="n">
         <v>708.9454665950478</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.01</v>
+        <v>-8.93</v>
       </c>
       <c r="L65" t="n">
-        <v>9.98</v>
+        <v>10.3</v>
       </c>
       <c r="M65" t="n">
         <v>1.61</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>7.89</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="H66" t="n">
-        <v>720.6</v>
+        <v>660.8</v>
       </c>
       <c r="I66" t="n">
         <v>664.9104327454627</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>1.59</v>
+        <v>-6.84</v>
       </c>
       <c r="L66" t="n">
-        <v>2.23</v>
+        <v>8.06</v>
       </c>
       <c r="M66" t="n">
-        <v>0.11</v>
+        <v>3.98</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O66" t="n">
         <v>1.79</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>12</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H67" t="n">
-        <v>678.75</v>
+        <v>683.95</v>
       </c>
       <c r="I67" t="n">
         <v>682.6141107548622</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.72</v>
+        <v>-3.5</v>
       </c>
       <c r="L67" t="n">
         <v>5.26</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H68" t="n">
-        <v>755.05</v>
+        <v>699.85</v>
       </c>
       <c r="I68" t="n">
         <v>730.5358232432623</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K68" t="n">
-        <v>10.4</v>
+        <v>2.32</v>
       </c>
       <c r="L68" t="n">
         <v>4.56</v>
       </c>
       <c r="M68" t="n">
-        <v>2.13</v>
+        <v>3.34</v>
       </c>
       <c r="N68" t="n">
-        <v>4.17</v>
+        <v>7.31</v>
       </c>
       <c r="O68" t="n">
         <v>0.77</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>13.94</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H69" t="n">
-        <v>526.75</v>
+        <v>544.2</v>
       </c>
       <c r="I69" t="n">
         <v>539.0849736099383</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K69" t="n">
-        <v>24.73</v>
+        <v>22.24</v>
       </c>
       <c r="L69" t="n">
         <v>12.35</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>6</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>9</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45681</v>
+        <v>45684</v>
       </c>
       <c r="H70" t="n">
-        <v>505.45</v>
+        <v>490.95</v>
       </c>
       <c r="I70" t="n">
         <v>499.2996306357874</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K70" t="n">
-        <v>-7.12</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>7.52</v>
+        <v>10.26</v>
       </c>
       <c r="M70" t="n">
         <v>0.73</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>10.97</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H71" t="n">
-        <v>455.15</v>
+        <v>468.2</v>
       </c>
       <c r="I71" t="n">
         <v>465.6952167455992</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>7.29</v>
+        <v>4.63</v>
       </c>
       <c r="L71" t="n">
         <v>5.88</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="H72" t="n">
-        <v>462.6</v>
+        <v>450.25</v>
       </c>
       <c r="I72" t="n">
         <v>457.4006074595892</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.2</v>
+        <v>-3.83</v>
       </c>
       <c r="L72" t="n">
-        <v>2.79</v>
+        <v>4.05</v>
       </c>
       <c r="M72" t="n">
         <v>5.69</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>9.43</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H73" t="n">
-        <v>434.35</v>
+        <v>454.35</v>
       </c>
       <c r="I73" t="n">
         <v>439.6873742100654</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>3.53</v>
+        <v>-0.91</v>
       </c>
       <c r="L73" t="n">
         <v>2.3</v>
@@ -4602,7 +5477,7 @@
         <v>4.65</v>
       </c>
       <c r="N73" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="O73" t="n">
         <v>-2.67</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>12.26</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45821</v>
+        <v>45824</v>
       </c>
       <c r="H74" t="n">
-        <v>490.25</v>
+        <v>472.75</v>
       </c>
       <c r="I74" t="n">
         <v>474.6127842957006</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K74" t="n">
-        <v>7.9</v>
+        <v>4.05</v>
       </c>
       <c r="L74" t="n">
         <v>4.03</v>
@@ -4659,7 +5546,7 @@
         <v>2.5</v>
       </c>
       <c r="N74" t="n">
-        <v>3.21</v>
+        <v>3.57</v>
       </c>
       <c r="O74" t="n">
         <v>4.6</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="H75" t="n">
-        <v>465.45</v>
+        <v>482.1</v>
       </c>
       <c r="I75" t="n">
         <v>473.4341524750611</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K75" t="n">
-        <v>1.54</v>
+        <v>-1.98</v>
       </c>
       <c r="L75" t="n">
         <v>3.99</v>
@@ -4716,7 +5615,7 @@
         <v>1.86</v>
       </c>
       <c r="N75" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="O75" t="n">
         <v>-3.57</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>9.02</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H76" t="n">
-        <v>470.2</v>
+        <v>457.35</v>
       </c>
       <c r="I76" t="n">
         <v>466.1491601885762</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.47</v>
+        <v>-5.13</v>
       </c>
       <c r="L76" t="n">
-        <v>4.63</v>
+        <v>6.42</v>
       </c>
       <c r="M76" t="n">
-        <v>0.26</v>
+        <v>1.9</v>
       </c>
       <c r="N76" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="O76" t="n">
         <v>3.58</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>7.31</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="H77" t="n">
-        <v>468.3</v>
+        <v>494.6</v>
       </c>
       <c r="I77" t="n">
         <v>490.7945879852228</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>-2.39</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>3.12</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M77" t="n">
         <v>1.65</v>
       </c>
       <c r="N77" t="n">
-        <v>1.3</v>
+        <v>5.62</v>
       </c>
       <c r="O77" t="n">
         <v>-2.73</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>10.36</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="H78" t="n">
-        <v>467.45</v>
+        <v>454.95</v>
       </c>
       <c r="I78" t="n">
         <v>461.2298387406058</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K78" t="n">
-        <v>-5.49</v>
+        <v>-8.02</v>
       </c>
       <c r="L78" t="n">
-        <v>7.17</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M78" t="n">
         <v>0.45</v>
       </c>
       <c r="N78" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="O78" t="n">
         <v>5.62</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>9.9</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H79" t="n">
-        <v>361.75</v>
+        <v>367.35</v>
       </c>
       <c r="I79" t="n">
         <v>363.2563876960618</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K79" t="n">
-        <v>20.49</v>
+        <v>19.25</v>
       </c>
       <c r="L79" t="n">
         <v>2.81</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>6.38</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="H80" t="n">
-        <v>354.15</v>
+        <v>350.55</v>
       </c>
       <c r="I80" t="n">
         <v>352.4436697554505</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K80" t="n">
-        <v>-3.59</v>
+        <v>-4.57</v>
       </c>
       <c r="L80" t="n">
-        <v>4.12</v>
+        <v>5.36</v>
       </c>
       <c r="M80" t="n">
         <v>0.55</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,25 +6008,25 @@
         <v>6.42</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H81" t="n">
-        <v>362.9</v>
+        <v>372.05</v>
       </c>
       <c r="I81" t="n">
         <v>364.953616389726</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K81" t="n">
-        <v>-3.52</v>
+        <v>-6.13</v>
       </c>
       <c r="L81" t="n">
-        <v>3.98</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M81" t="n">
-        <v>1.53</v>
+        <v>5.03</v>
       </c>
       <c r="N81" t="n">
         <v>5.3</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H82" t="n">
-        <v>370.6</v>
+        <v>351.2</v>
       </c>
       <c r="I82" t="n">
         <v>356.6451045085284</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.39</v>
+        <v>-5.6</v>
       </c>
       <c r="L82" t="n">
-        <v>4.45</v>
+        <v>5.9</v>
       </c>
       <c r="M82" t="n">
         <v>6.44</v>
       </c>
       <c r="N82" t="n">
-        <v>3.15</v>
+        <v>5.23</v>
       </c>
       <c r="O82" t="n">
         <v>2.52</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>12.63</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H83" t="n">
-        <v>308.7</v>
+        <v>334.75</v>
       </c>
       <c r="I83" t="n">
         <v>334.4966782043039</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K83" t="n">
-        <v>12.1</v>
+        <v>4.68</v>
       </c>
       <c r="L83" t="n">
         <v>3.62</v>
@@ -5172,7 +6167,7 @@
         <v>4.66</v>
       </c>
       <c r="N83" t="n">
-        <v>3.98</v>
+        <v>8.44</v>
       </c>
       <c r="O83" t="n">
         <v>-5.23</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>13.46</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H84" t="n">
-        <v>393.6</v>
+        <v>360.95</v>
       </c>
       <c r="I84" t="n">
         <v>364.3940493658733</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K84" t="n">
-        <v>17.58</v>
+        <v>7.83</v>
       </c>
       <c r="L84" t="n">
         <v>4.72</v>
@@ -5229,7 +6236,7 @@
         <v>3.09</v>
       </c>
       <c r="N84" t="n">
-        <v>3.16</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O84" t="n">
         <v>8.44</v>
@@ -5238,7 +6245,19 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>3</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -5265,28 +6284,28 @@
         <v>16.51</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H85" t="n">
-        <v>339.75</v>
+        <v>349.3</v>
       </c>
       <c r="I85" t="n">
         <v>345.1914995356273</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K85" t="n">
-        <v>5.87</v>
+        <v>3.23</v>
       </c>
       <c r="L85" t="n">
         <v>9.6</v>
       </c>
       <c r="M85" t="n">
-        <v>0.96</v>
+        <v>1.4</v>
       </c>
       <c r="N85" t="n">
-        <v>2.07</v>
+        <v>2.81</v>
       </c>
       <c r="O85" t="n">
         <v>-8.300000000000001</v>
@@ -5295,7 +6314,19 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -5322,22 +6353,22 @@
         <v>7.12</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="H86" t="n">
-        <v>330.2</v>
+        <v>322.8</v>
       </c>
       <c r="I86" t="n">
         <v>328.2781654266822</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K86" t="n">
-        <v>-5.47</v>
+        <v>-7.59</v>
       </c>
       <c r="L86" t="n">
-        <v>5.81</v>
+        <v>7.59</v>
       </c>
       <c r="M86" t="n">
         <v>5.89</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,14 @@
       <c r="Q87" t="n">
         <v>49</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10361,7 +11412,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="6">
@@ -10371,7 +11422,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -10381,7 +11432,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
@@ -10391,7 +11442,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10401,7 +11452,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -10411,7 +11462,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93.8</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -10421,7 +11472,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -10431,7 +11482,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -10441,7 +11492,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="14">
@@ -10451,7 +11502,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.63</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -10461,7 +11512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.24</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="16">
@@ -10471,7 +11522,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.97</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="17">
@@ -10481,7 +11532,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71.70999999999999</v>
+        <v>64.11</v>
       </c>
     </row>
     <row r="18">
@@ -10491,7 +11542,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.1</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="19">
@@ -10501,7 +11552,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.26</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="20">
@@ -10511,7 +11562,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.96</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="21">
@@ -10521,7 +11572,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.46</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="22">
@@ -10531,7 +11582,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -10541,7 +11592,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -10551,7 +11602,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="25">
@@ -10561,7 +11612,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.99</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="26">
@@ -10571,7 +11622,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.27</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="27">
@@ -10581,7 +11632,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.87</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="28">
@@ -10591,7 +11642,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
